--- a/templates/sanitized/guide-won.xlsx
+++ b/templates/sanitized/guide-won.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">세부내역!$A$1:$O$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">세부내역!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <customWorkbookViews>
     <customWorkbookView name="박수백 - 사용자 보기" guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" tabRatio="823" activeSheetId="1"/>
   </customWorkbookViews>
@@ -2567,9 +2567,8 @@
       <c r="B8" s="123" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="42" t="str">
+      <c r="C8" s="42">
         <f>"일금"&amp;NUMBERSTRING(H12,1)&amp;"원정(\"&amp;TEXT(H12,"###,##0")&amp;") V.A.T별도"</f>
-        <v>일금삼십사만삼천원정(\343,000) V.A.T별도</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="10"/>
@@ -2642,11 +2641,9 @@
       </c>
       <c r="G11" s="51">
         <f>세부내역!M25</f>
-        <v>343169</v>
       </c>
       <c r="H11" s="51">
         <f>F11*G11</f>
-        <v>343169</v>
       </c>
       <c r="I11" s="44"/>
       <c r="J11" s="2"/>
@@ -2663,7 +2660,6 @@
       <c r="G12" s="192"/>
       <c r="H12" s="192">
         <f>ROUNDDOWN(SUM(H11:H11),-3)</f>
-        <v>343000</v>
       </c>
       <c r="I12" s="193" t="s">
         <v>30</v>
@@ -2862,9 +2858,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" s="74" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A1" s="234" t="str">
+      <c r="A1" s="234">
         <f>"▣ 공사명 : "&amp;갑지!C5</f>
-        <v>▣ 공사명 : 설치 or 공사 끝맺음</v>
       </c>
       <c r="B1" s="234"/>
       <c r="C1" s="234"/>
@@ -3280,25 +3275,13 @@
       <c r="E6" s="56"/>
       <c r="F6" s="55"/>
       <c r="G6" s="182"/>
-      <c r="H6" s="177">
-        <f t="shared" ref="H6:H14" si="0">F6*G6</f>
-      </c>
+      <c r="H6" s="177"/>
       <c r="I6" s="22"/>
-      <c r="J6" s="22">
-        <f t="shared" ref="J6:J14" si="1">I6*F6</f>
-      </c>
-      <c r="K6" s="22">
-        <f t="shared" ref="K6:K14" si="2">INT(SUM((U6*V6),V6)*T6)</f>
-      </c>
-      <c r="L6" s="56">
-        <f t="shared" ref="L6:L14" si="3">F6*K6</f>
-      </c>
-      <c r="M6" s="22">
-        <f t="shared" ref="M6:M7" si="4">+J6+L6</f>
-      </c>
-      <c r="N6" s="188">
-        <f t="shared" ref="N6:N14" si="5">IFERROR((I6/G6)-1,"-")</f>
-      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="188"/>
       <c r="O6" s="127"/>
       <c r="P6" s="161"/>
       <c r="Q6" s="162"/>
@@ -3306,81 +3289,41 @@
       <c r="S6" s="164"/>
       <c r="T6" s="152"/>
       <c r="U6" s="165"/>
-      <c r="V6" s="151">
-        <f t="shared" ref="V6" si="6">SUM(X6,Z6,AB6,AD6,AF6,AH6,AJ6,AL6,AN6,AP6,AR6,AT6,AV6,AX6,AZ6,BB6,BD6)</f>
-      </c>
-      <c r="W6" s="166">
-        <f t="shared" ref="W6" si="7">0.7+0.59</f>
-      </c>
-      <c r="X6" s="151">
-        <f t="shared" ref="X6" si="8">W6*X$3</f>
-      </c>
-      <c r="Y6" s="166">
-        <f t="shared" ref="Y6" si="9">0.5+0.3+0.7+0.89</f>
-      </c>
-      <c r="Z6" s="151">
-        <f t="shared" ref="Z6" si="10">Y6*Z$3</f>
-      </c>
+      <c r="V6" s="151"/>
+      <c r="W6" s="166"/>
+      <c r="X6" s="151"/>
+      <c r="Y6" s="166"/>
+      <c r="Z6" s="151"/>
       <c r="AA6" s="166"/>
-      <c r="AB6" s="151">
-        <f t="shared" ref="AB6" si="11">AA6*AB$3</f>
-      </c>
+      <c r="AB6" s="151"/>
       <c r="AC6" s="166"/>
-      <c r="AD6" s="151">
-        <f t="shared" ref="AD6" si="12">AC6*AD$3</f>
-      </c>
+      <c r="AD6" s="151"/>
       <c r="AE6" s="167"/>
-      <c r="AF6" s="151">
-        <f t="shared" ref="AF6" si="13">AE6*AF$3</f>
-      </c>
+      <c r="AF6" s="151"/>
       <c r="AG6" s="168"/>
-      <c r="AH6" s="151">
-        <f t="shared" ref="AH6" si="14">AG6*AH$3</f>
-      </c>
+      <c r="AH6" s="151"/>
       <c r="AI6" s="168"/>
-      <c r="AJ6" s="151">
-        <f t="shared" ref="AJ6" si="15">AI6*AJ$3</f>
-      </c>
+      <c r="AJ6" s="151"/>
       <c r="AK6" s="168"/>
-      <c r="AL6" s="151">
-        <f t="shared" ref="AL6" si="16">AK6*AL$3</f>
-      </c>
+      <c r="AL6" s="151"/>
       <c r="AM6" s="168"/>
-      <c r="AN6" s="151">
-        <f t="shared" ref="AN6" si="17">AM6*AN$3</f>
-      </c>
+      <c r="AN6" s="151"/>
       <c r="AO6" s="168"/>
-      <c r="AP6" s="151">
-        <f t="shared" ref="AP6" si="18">AO6*AP$3</f>
-      </c>
+      <c r="AP6" s="151"/>
       <c r="AQ6" s="168"/>
-      <c r="AR6" s="151">
-        <f t="shared" ref="AR6" si="19">AQ6*AR$3</f>
-      </c>
+      <c r="AR6" s="151"/>
       <c r="AS6" s="168"/>
-      <c r="AT6" s="151">
-        <f t="shared" ref="AT6" si="20">AS6*AT$3</f>
-      </c>
+      <c r="AT6" s="151"/>
       <c r="AU6" s="168"/>
-      <c r="AV6" s="151">
-        <f t="shared" ref="AV6" si="21">AU6*AV$3</f>
-      </c>
+      <c r="AV6" s="151"/>
       <c r="AW6" s="168"/>
-      <c r="AX6" s="151">
-        <f t="shared" ref="AX6" si="22">AW6*AX$3</f>
-      </c>
+      <c r="AX6" s="151"/>
       <c r="AY6" s="168"/>
-      <c r="AZ6" s="151">
-        <f t="shared" ref="AZ6" si="23">AY6*AZ$3</f>
-      </c>
+      <c r="AZ6" s="151"/>
       <c r="BA6" s="167"/>
-      <c r="BB6" s="151">
-        <f t="shared" ref="BB6" si="24">BA6*BB$3</f>
-      </c>
+      <c r="BB6" s="151"/>
       <c r="BC6" s="169"/>
-      <c r="BD6" s="151">
-        <f t="shared" ref="BD6" si="25">BC6*BD$3</f>
-      </c>
+      <c r="BD6" s="151"/>
       <c r="BE6" s="170"/>
       <c r="BF6" s="170"/>
       <c r="BG6" s="170"/>
@@ -3394,36 +3337,20 @@
       <c r="BO6" s="170"/>
     </row>
     <row r="7" spans="1:71" ht="21" customHeight="1">
-      <c r="A7" s="79">
-        <f>A6+1</f>
-      </c>
+      <c r="A7" s="79"/>
       <c r="B7" s="25"/>
       <c r="C7" s="73"/>
       <c r="D7" s="139"/>
       <c r="E7" s="57"/>
-      <c r="F7" s="55">
-        <f>F6</f>
-      </c>
+      <c r="F7" s="55"/>
       <c r="G7" s="182"/>
-      <c r="H7" s="177">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H7" s="177"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="22">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K7" s="22">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="L7" s="56">
-        <f t="shared" si="3"/>
-      </c>
-      <c r="M7" s="22">
-        <f t="shared" si="4"/>
-      </c>
-      <c r="N7" s="188">
-        <f t="shared" si="5"/>
-      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="188"/>
       <c r="O7" s="128"/>
       <c r="P7" s="171"/>
       <c r="Q7" s="160"/>
@@ -3467,36 +3394,20 @@
       <c r="BD7" s="160"/>
     </row>
     <row r="8" spans="1:71" ht="21" customHeight="1">
-      <c r="A8" s="79">
-        <f t="shared" ref="A8:A14" si="26">A7+1</f>
-      </c>
+      <c r="A8" s="79"/>
       <c r="B8" s="25"/>
       <c r="C8" s="73"/>
       <c r="D8" s="139"/>
       <c r="E8" s="57"/>
-      <c r="F8" s="55">
-        <f>F6</f>
-      </c>
+      <c r="F8" s="55"/>
       <c r="G8" s="182"/>
-      <c r="H8" s="177">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H8" s="177"/>
       <c r="I8" s="23"/>
-      <c r="J8" s="22">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K8" s="22">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="L8" s="56">
-        <f t="shared" si="3"/>
-      </c>
-      <c r="M8" s="22">
-        <f t="shared" ref="M8:M14" si="27">+J8+L8</f>
-      </c>
-      <c r="N8" s="188">
-        <f t="shared" si="5"/>
-      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="188"/>
       <c r="O8" s="128"/>
       <c r="P8" s="171"/>
       <c r="Q8" s="160"/>
@@ -3540,36 +3451,20 @@
       <c r="BD8" s="160"/>
     </row>
     <row r="9" spans="1:71" ht="21" customHeight="1">
-      <c r="A9" s="79">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="A9" s="79"/>
       <c r="B9" s="54"/>
       <c r="C9" s="73"/>
       <c r="D9" s="139"/>
       <c r="E9" s="57"/>
-      <c r="F9" s="55">
-        <f>F6</f>
-      </c>
+      <c r="F9" s="55"/>
       <c r="G9" s="182"/>
-      <c r="H9" s="177">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H9" s="177"/>
       <c r="I9" s="22"/>
-      <c r="J9" s="22">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K9" s="22">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="L9" s="56">
-        <f t="shared" si="3"/>
-      </c>
-      <c r="M9" s="22">
-        <f t="shared" si="27"/>
-      </c>
-      <c r="N9" s="188">
-        <f t="shared" si="5"/>
-      </c>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="188"/>
       <c r="O9" s="129"/>
       <c r="P9" s="171"/>
       <c r="Q9" s="160"/>
@@ -3613,36 +3508,20 @@
       <c r="BD9" s="160"/>
     </row>
     <row r="10" spans="1:71" ht="21" customHeight="1">
-      <c r="A10" s="79">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="A10" s="79"/>
       <c r="B10" s="73"/>
       <c r="C10" s="77"/>
       <c r="D10" s="140"/>
       <c r="E10" s="53"/>
-      <c r="F10" s="59">
-        <f>F6</f>
-      </c>
+      <c r="F10" s="59"/>
       <c r="G10" s="182"/>
-      <c r="H10" s="177">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H10" s="177"/>
       <c r="I10" s="22"/>
-      <c r="J10" s="22">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K10" s="22">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="L10" s="56">
-        <f t="shared" si="3"/>
-      </c>
-      <c r="M10" s="22">
-        <f t="shared" si="27"/>
-      </c>
-      <c r="N10" s="188">
-        <f t="shared" si="5"/>
-      </c>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="188"/>
       <c r="O10" s="129"/>
       <c r="P10" s="172"/>
       <c r="Q10" s="160"/>
@@ -3687,36 +3566,20 @@
       <c r="BP10" s="86"/>
     </row>
     <row r="11" spans="1:71" ht="21" customHeight="1">
-      <c r="A11" s="79">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="A11" s="79"/>
       <c r="B11" s="54"/>
       <c r="C11" s="60"/>
       <c r="D11" s="141"/>
       <c r="E11" s="56"/>
-      <c r="F11" s="55">
-        <f>F6</f>
-      </c>
+      <c r="F11" s="55"/>
       <c r="G11" s="182"/>
-      <c r="H11" s="177">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H11" s="177"/>
       <c r="I11" s="22"/>
-      <c r="J11" s="22">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K11" s="22">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="L11" s="56">
-        <f t="shared" si="3"/>
-      </c>
-      <c r="M11" s="22">
-        <f t="shared" si="27"/>
-      </c>
-      <c r="N11" s="188">
-        <f t="shared" si="5"/>
-      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="188"/>
       <c r="O11" s="129"/>
       <c r="P11" s="173"/>
       <c r="Q11" s="160"/>
@@ -3761,36 +3624,20 @@
       <c r="BP11" s="85"/>
     </row>
     <row r="12" spans="1:71" s="27" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="79">
-        <f t="shared" si="26"/>
-      </c>
+      <c r="A12" s="79"/>
       <c r="B12" s="70"/>
       <c r="C12" s="95"/>
       <c r="D12" s="142"/>
       <c r="E12" s="78"/>
-      <c r="F12" s="59">
-        <f>F6*2</f>
-      </c>
+      <c r="F12" s="59"/>
       <c r="G12" s="182"/>
-      <c r="H12" s="177">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H12" s="177"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="22">
-        <f t="shared" si="1"/>
-      </c>
-      <c r="K12" s="22">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="L12" s="56">
-        <f t="shared" si="3"/>
-      </c>
-      <c r="M12" s="22">
-        <f t="shared" si="27"/>
-      </c>
-      <c r="N12" s="188">
-        <f t="shared" si="5"/>
-      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="188"/>
       <c r="O12" s="130"/>
       <c r="P12" s="174"/>
       <c r="Q12" s="157"/>
@@ -3836,8 +3683,7 @@
     </row>
     <row r="13" spans="1:71" s="27" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="79">
-        <f t="shared" si="26"/>
-        <v>8</v>
+        <f>A12+1</f>
       </c>
       <c r="B13" s="70" t="s">
         <v>23</v>
@@ -3854,32 +3700,25 @@
       </c>
       <c r="G13" s="183"/>
       <c r="H13" s="177">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>F13*G13</f>
       </c>
       <c r="I13" s="53">
         <f>J12*40%</f>
-        <v>4800</v>
       </c>
       <c r="J13" s="22">
-        <f t="shared" si="1"/>
-        <v>4800</v>
+        <f>I13*F13</f>
       </c>
       <c r="K13" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>INT(SUM((U13*V13),V13)*T13)</f>
       </c>
       <c r="L13" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>F13*K13</f>
       </c>
       <c r="M13" s="22">
-        <f t="shared" si="27"/>
-        <v>4800</v>
-      </c>
-      <c r="N13" s="188" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
+        <f>+J13+L13</f>
+      </c>
+      <c r="N13" s="188">
+        <f>IFERROR((I13/G13)-1,"-")</f>
       </c>
       <c r="O13" s="129"/>
       <c r="P13" s="174"/>
@@ -3926,8 +3765,7 @@
     </row>
     <row r="14" spans="1:71" ht="21" customHeight="1">
       <c r="A14" s="97">
-        <f t="shared" si="26"/>
-        <v>9</v>
+        <f>A13+1</f>
       </c>
       <c r="B14" s="68" t="s">
         <v>16</v>
@@ -3944,35 +3782,27 @@
       </c>
       <c r="G14" s="184">
         <f>INT(SUM(H6:H13)*2%)</f>
-        <v>0</v>
       </c>
       <c r="H14" s="190">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>F14*G14</f>
       </c>
       <c r="I14" s="91">
         <f>INT(SUM(J6:J13)*2%)</f>
-        <v>336</v>
       </c>
       <c r="J14" s="26">
-        <f t="shared" si="1"/>
-        <v>336</v>
+        <f>I14*F14</f>
       </c>
       <c r="K14" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>INT(SUM((U14*V14),V14)*T14)</f>
       </c>
       <c r="L14" s="61">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>F14*K14</f>
       </c>
       <c r="M14" s="26">
-        <f t="shared" si="27"/>
-        <v>336</v>
-      </c>
-      <c r="N14" s="189" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
+        <f>+J14+L14</f>
+      </c>
+      <c r="N14" s="189">
+        <f>IFERROR((I14/G14)-1,"-")</f>
       </c>
       <c r="O14" s="131"/>
       <c r="P14" s="175"/>
@@ -4029,25 +3859,20 @@
       <c r="G15" s="204"/>
       <c r="H15" s="204">
         <f>SUM(H6:H14)</f>
-        <v>0</v>
       </c>
       <c r="I15" s="205"/>
       <c r="J15" s="205">
         <f>SUM(J6:J14)</f>
-        <v>17136</v>
       </c>
       <c r="K15" s="205"/>
       <c r="L15" s="205">
         <f>SUM(L6:L14)</f>
-        <v>288221</v>
       </c>
       <c r="M15" s="205">
         <f>SUM(M6:M14)</f>
-        <v>305357</v>
-      </c>
-      <c r="N15" s="206" t="e">
+      </c>
+      <c r="N15" s="206">
         <f>AVERAGE(N6:N14)</f>
-        <v>#DIV/0!</v>
       </c>
       <c r="O15" s="207"/>
       <c r="P15" s="87"/>
@@ -4154,7 +3979,6 @@
       <c r="L17" s="22"/>
       <c r="M17" s="22">
         <f>INT(M15*F17)</f>
-        <v>18321</v>
       </c>
       <c r="N17" s="182"/>
       <c r="O17" s="133"/>
@@ -4239,7 +4063,6 @@
       <c r="L18" s="102"/>
       <c r="M18" s="22">
         <f>INT(M15*F18)</f>
-        <v>6320</v>
       </c>
       <c r="N18" s="182"/>
       <c r="O18" s="133"/>
@@ -4324,7 +4147,6 @@
       <c r="L19" s="102"/>
       <c r="M19" s="22">
         <f>INT(L15*F19)</f>
-        <v>13171</v>
       </c>
       <c r="N19" s="182"/>
       <c r="O19" s="133"/>
@@ -4745,7 +4567,6 @@
       <c r="L24" s="213"/>
       <c r="M24" s="213">
         <f>SUM(M17:M23)</f>
-        <v>37812</v>
       </c>
       <c r="N24" s="211"/>
       <c r="O24" s="214"/>
@@ -4822,7 +4643,6 @@
       <c r="L25" s="194"/>
       <c r="M25" s="198">
         <f>M15+M24</f>
-        <v>343169</v>
       </c>
       <c r="N25" s="199"/>
       <c r="O25" s="200"/>

--- a/templates/sanitized/guide-won.xlsx
+++ b/templates/sanitized/guide-won.xlsx
@@ -2799,16 +2799,6 @@
     </row>
     <row r="22" spans="1:14" ht="10.199999999999999" customHeight="1"/>
   </sheetData>
-  <customSheetViews>
-    <customSheetView guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview">
-      <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-      <printOptions horizontalCentered="1"/>
-      <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-      <headerFooter scaleWithDoc="0">
-        <oddFooter>&amp;C&amp;P / &amp;N&amp;R㈜서울영상테크</oddFooter>
-      </headerFooter>
-    </customSheetView>
-  </customSheetViews>
   <mergeCells count="5">
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B19:B20"/>
@@ -5209,18 +5199,6 @@
     <row r="418" ht="21" customHeight="1"/>
     <row r="419" ht="21" customHeight="1"/>
   </sheetData>
-  <customSheetViews>
-    <customSheetView guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview">
-      <pane xSplit="5" ySplit="3" topLeftCell="F4" activePane="bottomRight" state="frozen"/>
-      <selection pane="bottomRight" activeCell="B16" sqref="B16"/>
-      <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.51181102362204722" header="0.31496062992125984" footer="0.31496062992125984"/>
-      <printOptions horizontalCentered="1"/>
-      <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape"/>
-      <headerFooter scaleWithDoc="0">
-        <oddFooter>&amp;C&amp;P / &amp;N&amp;R㈜서울영상테크</oddFooter>
-      </headerFooter>
-    </customSheetView>
-  </customSheetViews>
   <mergeCells count="37">
     <mergeCell ref="BC2:BD2"/>
     <mergeCell ref="AS2:AT2"/>
